--- a/branches/feature/term-test/ValueSet-mii-vs-kardio-extended-condition-severity-snomedct.xlsx
+++ b/branches/feature/term-test/ValueSet-mii-vs-kardio-extended-condition-severity-snomedct.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T12:43:58+00:00</t>
+    <t>2026-09-15T13:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature/term-test/ValueSet-mii-vs-kardio-extended-condition-severity-snomedct.xlsx
+++ b/branches/feature/term-test/ValueSet-mii-vs-kardio-extended-condition-severity-snomedct.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T13:04:36+00:00</t>
+    <t>2026-09-15T14:40:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature/term-test/ValueSet-mii-vs-kardio-extended-condition-severity-snomedct.xlsx
+++ b/branches/feature/term-test/ValueSet-mii-vs-kardio-extended-condition-severity-snomedct.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:40:08+00:00</t>
+    <t>2026-09-15T15:28:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature/term-test/ValueSet-mii-vs-kardio-extended-condition-severity-snomedct.xlsx
+++ b/branches/feature/term-test/ValueSet-mii-vs-kardio-extended-condition-severity-snomedct.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:28:24+00:00</t>
+    <t>2026-09-15T15:41:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
